--- a/artfynd/A 8885-2024 artfynd.xlsx
+++ b/artfynd/A 8885-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>127746717</v>
       </c>
       <c r="B3" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127746720</v>
       </c>
       <c r="B4" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8885-2024 artfynd.xlsx
+++ b/artfynd/A 8885-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127746721</v>
       </c>
       <c r="B2" t="n">
-        <v>82861</v>
+        <v>82864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127746717</v>
       </c>
       <c r="B3" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127746720</v>
       </c>
       <c r="B4" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127746722</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 8885-2024 artfynd.xlsx
+++ b/artfynd/A 8885-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127746721</v>
       </c>
       <c r="B2" t="n">
-        <v>82864</v>
+        <v>82870</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127746717</v>
       </c>
       <c r="B3" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127746720</v>
       </c>
       <c r="B4" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127746722</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 8885-2024 artfynd.xlsx
+++ b/artfynd/A 8885-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>127746717</v>
       </c>
       <c r="B3" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127746720</v>
       </c>
       <c r="B4" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8885-2024 artfynd.xlsx
+++ b/artfynd/A 8885-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>127746717</v>
       </c>
       <c r="B3" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127746720</v>
       </c>
       <c r="B4" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8885-2024 artfynd.xlsx
+++ b/artfynd/A 8885-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>127746717</v>
       </c>
       <c r="B3" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127746720</v>
       </c>
       <c r="B4" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8885-2024 artfynd.xlsx
+++ b/artfynd/A 8885-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127746721</v>
       </c>
       <c r="B2" t="n">
-        <v>82870</v>
+        <v>82873</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127746717</v>
       </c>
       <c r="B3" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127746720</v>
       </c>
       <c r="B4" t="n">
-        <v>91317</v>
+        <v>91325</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127746722</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 8885-2024 artfynd.xlsx
+++ b/artfynd/A 8885-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127746721</v>
       </c>
       <c r="B2" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127746717</v>
       </c>
       <c r="B3" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127746720</v>
       </c>
       <c r="B4" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127746722</v>
       </c>
       <c r="B5" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 8885-2024 artfynd.xlsx
+++ b/artfynd/A 8885-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127746721</v>
       </c>
       <c r="B2" t="n">
-        <v>82942</v>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127746717</v>
+        <v>127746720</v>
       </c>
       <c r="B3" t="n">
-        <v>91470</v>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612937</v>
+        <v>612837</v>
       </c>
       <c r="R3" t="n">
-        <v>7028236</v>
+        <v>7028166</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,45 +869,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127746720</v>
+        <v>127746722</v>
       </c>
       <c r="B4" t="n">
-        <v>91417</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rämmasjötjärnen, ån, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612837</v>
+        <v>612755</v>
       </c>
       <c r="R4" t="n">
-        <v>7028166</v>
+        <v>7028193</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -942,6 +950,11 @@
           <t>2025-08-22</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>i 3 gamla granar</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -963,116 +976,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>127746722</v>
-      </c>
-      <c r="B5" t="n">
-        <v>57685</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Rämmasjötjärnen, ån, Ång</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>612755</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7028193</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Resele</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>i 3 gamla granar</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8885-2024 artfynd.xlsx
+++ b/artfynd/A 8885-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127746721</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127746720</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,8 +991,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127746722</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>